--- a/docs/downloads/20260820_Seputeh Hills_Teduh Weekly Update.xlsx
+++ b/docs/downloads/20260820_Seputeh Hills_Teduh Weekly Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,10 @@
     <col width="9" customWidth="1" min="19" max="19"/>
     <col width="9" customWidth="1" min="20" max="20"/>
     <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="42" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="42" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -543,8 +546,11 @@
       <c r="P3" s="3" t="n">
         <v>46241</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="S3" s="3" t="n">
         <v>46248</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>46255</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -640,22 +646,37 @@
           <t>%</t>
         </is>
       </c>
-      <c r="S4" s="6" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="U4" s="6" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="X4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -729,18 +750,29 @@
         <f>Q5/$F$5</f>
         <v/>
       </c>
-      <c r="S5" s="12">
+      <c r="S5" s="10">
         <f>T5-Q5</f>
         <v/>
       </c>
-      <c r="T5" s="12" t="n">
+      <c r="T5" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="U5" s="13">
+      <c r="U5" s="11">
         <f>T5/$F$5</f>
         <v/>
       </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="V5" s="12">
+        <f>W5-T5</f>
+        <v/>
+      </c>
+      <c r="W5" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="X5" s="13">
+        <f>W5/$F$5</f>
+        <v/>
+      </c>
+      <c r="Y5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -814,18 +846,29 @@
         <f>Q6/$F$6</f>
         <v/>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="10">
         <f>T6-Q6</f>
         <v/>
       </c>
-      <c r="T6" s="12" t="n">
+      <c r="T6" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="U6" s="13">
+      <c r="U6" s="11">
         <f>T6/$F$6</f>
         <v/>
       </c>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="V6" s="12">
+        <f>W6-T6</f>
+        <v/>
+      </c>
+      <c r="W6" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="X6" s="13">
+        <f>W6/$F$6</f>
+        <v/>
+      </c>
+      <c r="Y6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -899,18 +942,29 @@
         <f>Q7/$F$7</f>
         <v/>
       </c>
-      <c r="S7" s="12">
+      <c r="S7" s="10">
         <f>T7-Q7</f>
         <v/>
       </c>
-      <c r="T7" s="12" t="n">
+      <c r="T7" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="U7" s="13">
+      <c r="U7" s="11">
         <f>T7/$F$7</f>
         <v/>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="V7" s="12">
+        <f>W7-T7</f>
+        <v/>
+      </c>
+      <c r="W7" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="X7" s="13">
+        <f>W7/$F$7</f>
+        <v/>
+      </c>
+      <c r="Y7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -984,18 +1038,29 @@
         <f>Q8/$F$8</f>
         <v/>
       </c>
-      <c r="S8" s="12">
+      <c r="S8" s="10">
         <f>T8-Q8</f>
         <v/>
       </c>
-      <c r="T8" s="12" t="n">
+      <c r="T8" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="U8" s="13">
+      <c r="U8" s="11">
         <f>T8/$F$8</f>
         <v/>
       </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="V8" s="12">
+        <f>W8-T8</f>
+        <v/>
+      </c>
+      <c r="W8" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="X8" s="13">
+        <f>W8/$F$8</f>
+        <v/>
+      </c>
+      <c r="Y8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -1069,18 +1134,29 @@
         <f>Q9/$F$9</f>
         <v/>
       </c>
-      <c r="S9" s="12">
+      <c r="S9" s="10">
         <f>T9-Q9</f>
         <v/>
       </c>
-      <c r="T9" s="12" t="n">
+      <c r="T9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U9" s="13">
+      <c r="U9" s="11">
         <f>T9/$F$9</f>
         <v/>
       </c>
-      <c r="V9" s="8" t="inlineStr">
+      <c r="V9" s="12">
+        <f>W9-T9</f>
+        <v/>
+      </c>
+      <c r="W9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="13">
+        <f>W9/$F$9</f>
+        <v/>
+      </c>
+      <c r="Y9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1144,28 +1220,40 @@
         <f>Q10/$F$10</f>
         <v/>
       </c>
-      <c r="S10" s="12">
+      <c r="S10" s="10">
         <f>T10-Q10</f>
         <v/>
       </c>
-      <c r="T10" s="12" t="n">
+      <c r="T10" s="10" t="n">
         <v>306</v>
       </c>
-      <c r="U10" s="13">
+      <c r="U10" s="11">
         <f>T10/$F$10</f>
         <v/>
       </c>
-      <c r="V10" s="8" t="inlineStr">
+      <c r="V10" s="12">
+        <f>W10-T10</f>
+        <v/>
+      </c>
+      <c r="W10" s="12" t="n">
+        <v>335</v>
+      </c>
+      <c r="X10" s="13">
+        <f>W10/$F$10</f>
+        <v/>
+      </c>
+      <c r="Y10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="G3:I3"/>
+    <mergeCell ref="V3:X3"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="P3:R3"/>
   </mergeCells>
